--- a/files/R01-R69全节点业务验收测试包/M00_项目主数据与总目录/M00_M00-MASTER-001_TEST-M00-002_项目主数据.xlsx
+++ b/files/R01-R69全节点业务验收测试包/M00_项目主数据与总目录/M00_M00-MASTER-001_TEST-M00-002_项目主数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目" sheetId="1" r:id="R0ae61a406d1b457b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管线" sheetId="2" r:id="R06d3251d74994cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="焊口" sheetId="3" r:id="R9ef6889c33a941d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料" sheetId="4" r:id="Re037610bc64840b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身份引用" sheetId="5" r:id="R66ef87a6cf8e4234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目" sheetId="1" r:id="R0f974b185c6942ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管线" sheetId="2" r:id="R9d224fb5db9646a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="焊口" sheetId="3" r:id="R5b1f6a0736d94eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料" sheetId="4" r:id="R4a8de7426ec748de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身份引用" sheetId="5" r:id="Rc9f30bc44e7f4d5f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,7 +46,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -63,8 +63,13 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left/>
@@ -89,6 +94,58 @@
       <x:bottom/>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:top/>
     </x:border>
     <x:border>
@@ -98,7 +155,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -172,24 +229,88 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -304,6 +425,166 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="fe302664-5b47-4282-994a-198a885701bb"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1cbc35cacf8f4624"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="029a0c26-57fc-484a-8f49-da96b1d1afc8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5a0a7bf2213848b1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="35d5f615-21f7-4e10-8f3c-64ef7a84dd5c"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R64e34d4e88f4481f"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="32d4d83d-5be3-459d-94b0-8cffc07da39d"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf6f282679cc94b85"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="e80f04dd-8719-4827-af79-ea1aecf00868"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R88491ad4b21446f8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -503,6 +784,9 @@
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" hidden="0" customHeight="1">
@@ -510,12 +794,18 @@
         <x:v>项目主数据</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>测试专用／合成资料／不得用于真实工程｜TEST-ONLY / SYNTHETIC / NOT FOR REAL ENGINEERING USE｜文件编号：TEST-M00-002｜版本：0｜日期：2026-07-15</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
+      <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
     </x:row>
     <x:row r="3"/>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -571,15 +861,47 @@
         <x:v>资料包日期</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
     </x:row>
     <x:row r="11"/>
-    <x:row r="12"/>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="52" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B12" s="53"/>
+      <x:c r="C12" s="53"/>
+      <x:c r="D12" s="53"/>
+      <x:c r="E12" s="54"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="55"/>
+      <x:c r="B13" s="56"/>
+      <x:c r="C13" s="56"/>
+      <x:c r="D13" s="56"/>
+      <x:c r="E13" s="57"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="55"/>
+      <x:c r="B14" s="56"/>
+      <x:c r="C14" s="56"/>
+      <x:c r="D14" s="56"/>
+      <x:c r="E14" s="57"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="58"/>
+      <x:c r="B15" s="59"/>
+      <x:c r="C15" s="59"/>
+      <x:c r="D15" s="59"/>
+      <x:c r="E15" s="60"/>
+    </x:row>
+    <x:row r="16"/>
+    <x:row r="17"/>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:B1"/>
-    <x:mergeCell ref="A2:B2"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A12:C12"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:B10">
     <x:cfRule type="expression" dxfId="0" priority="1">
@@ -590,6 +912,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44826ecdf2334239"/>
 </x:worksheet>
 </file>
 
@@ -650,16 +973,16 @@
       <x:c r="A5" s="27" t="str">
         <x:v>PL8301</x:v>
       </x:c>
-      <x:c r="B5" s="38" t="str">
+      <x:c r="B5" s="66" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C5" s="38" t="str">
+      <x:c r="C5" s="66" t="str">
         <x:v>Φ108×4</x:v>
       </x:c>
-      <x:c r="D5" s="38" t="n">
+      <x:c r="D5" s="66" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E5" s="38" t="n">
+      <x:c r="E5" s="66" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F5" s="28" t="str">
@@ -670,16 +993,16 @@
       <x:c r="A6" s="29" t="str">
         <x:v>PL8302</x:v>
       </x:c>
-      <x:c r="B6" s="39" t="str">
+      <x:c r="B6" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C6" s="39" t="str">
+      <x:c r="C6" s="67" t="str">
         <x:v>Φ108×4</x:v>
       </x:c>
-      <x:c r="D6" s="39" t="n">
+      <x:c r="D6" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E6" s="39" t="n">
+      <x:c r="E6" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F6" s="30" t="str">
@@ -690,16 +1013,16 @@
       <x:c r="A7" s="29" t="str">
         <x:v>PL8303</x:v>
       </x:c>
-      <x:c r="B7" s="39" t="str">
+      <x:c r="B7" s="67" t="str">
         <x:v>B00/S02</x:v>
       </x:c>
-      <x:c r="C7" s="39" t="str">
+      <x:c r="C7" s="67" t="str">
         <x:v>Φ108×4 / 测试段Φ108×4.5</x:v>
       </x:c>
-      <x:c r="D7" s="39" t="n">
+      <x:c r="D7" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E7" s="39" t="n">
+      <x:c r="E7" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F7" s="30" t="str">
@@ -710,16 +1033,16 @@
       <x:c r="A8" s="29" t="str">
         <x:v>PL8304</x:v>
       </x:c>
-      <x:c r="B8" s="39" t="str">
+      <x:c r="B8" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C8" s="39" t="str">
+      <x:c r="C8" s="67" t="str">
         <x:v>Φ108×4</x:v>
       </x:c>
-      <x:c r="D8" s="39" t="n">
+      <x:c r="D8" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E8" s="39" t="n">
+      <x:c r="E8" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F8" s="30" t="str">
@@ -730,16 +1053,16 @@
       <x:c r="A9" s="29" t="str">
         <x:v>PL8305</x:v>
       </x:c>
-      <x:c r="B9" s="39" t="str">
+      <x:c r="B9" s="67" t="str">
         <x:v>B00/S05</x:v>
       </x:c>
-      <x:c r="C9" s="39" t="str">
+      <x:c r="C9" s="67" t="str">
         <x:v>Φ108×4</x:v>
       </x:c>
-      <x:c r="D9" s="39" t="n">
+      <x:c r="D9" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E9" s="39" t="n">
+      <x:c r="E9" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F9" s="30" t="str">
@@ -750,16 +1073,16 @@
       <x:c r="A10" s="29" t="str">
         <x:v>PL8306</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="str">
+      <x:c r="B10" s="67" t="str">
         <x:v>B00/S06</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="str">
+      <x:c r="C10" s="67" t="str">
         <x:v>Φ108×4</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F10" s="30" t="str">
@@ -770,16 +1093,16 @@
       <x:c r="A11" s="29" t="str">
         <x:v>VT8301</x:v>
       </x:c>
-      <x:c r="B11" s="39" t="str">
+      <x:c r="B11" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C11" s="39" t="str">
+      <x:c r="C11" s="67" t="str">
         <x:v>Φ57×3.5</x:v>
       </x:c>
-      <x:c r="D11" s="39" t="n">
+      <x:c r="D11" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E11" s="39" t="n">
+      <x:c r="E11" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F11" s="30" t="str">
@@ -790,16 +1113,16 @@
       <x:c r="A12" s="29" t="str">
         <x:v>VT8302</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="str">
+      <x:c r="B12" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="str">
+      <x:c r="C12" s="67" t="str">
         <x:v>Φ57×3.5</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
+      <x:c r="D12" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F12" s="30" t="str">
@@ -810,16 +1133,16 @@
       <x:c r="A13" s="29" t="str">
         <x:v>PL8307-TEST</x:v>
       </x:c>
-      <x:c r="B13" s="39" t="str">
+      <x:c r="B13" s="67" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="C13" s="39" t="str">
+      <x:c r="C13" s="67" t="str">
         <x:v>Φ89×4.5</x:v>
       </x:c>
-      <x:c r="D13" s="39" t="n">
+      <x:c r="D13" s="67" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E13" s="39" t="n">
+      <x:c r="E13" s="67" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F13" s="30" t="str">
@@ -830,16 +1153,16 @@
       <x:c r="A14" s="29" t="str">
         <x:v>ST8301-TEST</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="str">
+      <x:c r="B14" s="67" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="str">
+      <x:c r="C14" s="67" t="str">
         <x:v>Φ76×16</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="67" t="n">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="67" t="n">
         <x:v>300</x:v>
       </x:c>
       <x:c r="F14" s="30" t="str">
@@ -850,16 +1173,16 @@
       <x:c r="A15" s="31" t="str">
         <x:v>PL8308-TEST</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="str">
+      <x:c r="B15" s="68" t="str">
         <x:v>S04</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="str">
+      <x:c r="C15" s="68" t="str">
         <x:v>Φ108×4；套管Φ273×7</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="68" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="68" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
@@ -867,11 +1190,47 @@
       </x:c>
     </x:row>
     <x:row r="16"/>
-    <x:row r="17"/>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="52" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B17" s="53"/>
+      <x:c r="C17" s="53"/>
+      <x:c r="D17" s="53"/>
+      <x:c r="E17" s="53"/>
+      <x:c r="F17" s="54"/>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="55"/>
+      <x:c r="B18" s="56"/>
+      <x:c r="C18" s="56"/>
+      <x:c r="D18" s="56"/>
+      <x:c r="E18" s="56"/>
+      <x:c r="F18" s="57"/>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="55"/>
+      <x:c r="B19" s="56"/>
+      <x:c r="C19" s="56"/>
+      <x:c r="D19" s="56"/>
+      <x:c r="E19" s="56"/>
+      <x:c r="F19" s="57"/>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="58"/>
+      <x:c r="B20" s="59"/>
+      <x:c r="C20" s="59"/>
+      <x:c r="D20" s="59"/>
+      <x:c r="E20" s="59"/>
+      <x:c r="F20" s="60"/>
+    </x:row>
+    <x:row r="21"/>
+    <x:row r="22"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A17:C17"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:F15">
     <x:cfRule type="expression" dxfId="2" priority="1">
@@ -882,6 +1241,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3227c17fa54520"/>
 </x:worksheet>
 </file>
 
@@ -948,19 +1308,19 @@
       <x:c r="A5" s="27" t="str">
         <x:v>W-B00-001</x:v>
       </x:c>
-      <x:c r="B5" s="38" t="str">
+      <x:c r="B5" s="66" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C5" s="38" t="str">
+      <x:c r="C5" s="66" t="str">
         <x:v>PL8301</x:v>
       </x:c>
-      <x:c r="D5" s="38" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E5" s="38" t="str">
+      <x:c r="D5" s="66" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E5" s="66" t="str">
         <x:v>2026-05-11</x:v>
       </x:c>
-      <x:c r="F5" s="38" t="str">
+      <x:c r="F5" s="66" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G5" s="28" t="n">
@@ -971,19 +1331,19 @@
       <x:c r="A6" s="29" t="str">
         <x:v>W-B00-002</x:v>
       </x:c>
-      <x:c r="B6" s="39" t="str">
+      <x:c r="B6" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C6" s="39" t="str">
+      <x:c r="C6" s="67" t="str">
         <x:v>PL8301</x:v>
       </x:c>
-      <x:c r="D6" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E6" s="39" t="str">
+      <x:c r="D6" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E6" s="67" t="str">
         <x:v>2026-05-11</x:v>
       </x:c>
-      <x:c r="F6" s="39" t="str">
+      <x:c r="F6" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G6" s="30" t="n">
@@ -994,19 +1354,19 @@
       <x:c r="A7" s="29" t="str">
         <x:v>W-B00-003</x:v>
       </x:c>
-      <x:c r="B7" s="39" t="str">
+      <x:c r="B7" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C7" s="39" t="str">
+      <x:c r="C7" s="67" t="str">
         <x:v>PL8302</x:v>
       </x:c>
-      <x:c r="D7" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E7" s="39" t="str">
+      <x:c r="D7" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E7" s="67" t="str">
         <x:v>2026-05-12</x:v>
       </x:c>
-      <x:c r="F7" s="39" t="str">
+      <x:c r="F7" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G7" s="30" t="n">
@@ -1017,19 +1377,19 @@
       <x:c r="A8" s="29" t="str">
         <x:v>W-B00-004</x:v>
       </x:c>
-      <x:c r="B8" s="39" t="str">
+      <x:c r="B8" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C8" s="39" t="str">
+      <x:c r="C8" s="67" t="str">
         <x:v>PL8302</x:v>
       </x:c>
-      <x:c r="D8" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E8" s="39" t="str">
+      <x:c r="D8" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E8" s="67" t="str">
         <x:v>2026-05-12</x:v>
       </x:c>
-      <x:c r="F8" s="39" t="str">
+      <x:c r="F8" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G8" s="30" t="n">
@@ -1040,19 +1400,19 @@
       <x:c r="A9" s="29" t="str">
         <x:v>W-B00-005</x:v>
       </x:c>
-      <x:c r="B9" s="39" t="str">
+      <x:c r="B9" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C9" s="39" t="str">
+      <x:c r="C9" s="67" t="str">
         <x:v>PL8303</x:v>
       </x:c>
-      <x:c r="D9" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E9" s="39" t="str">
+      <x:c r="D9" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E9" s="67" t="str">
         <x:v>2026-05-13</x:v>
       </x:c>
-      <x:c r="F9" s="39" t="str">
+      <x:c r="F9" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G9" s="30" t="n">
@@ -1063,19 +1423,19 @@
       <x:c r="A10" s="29" t="str">
         <x:v>W-B00-006</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="str">
+      <x:c r="B10" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="str">
+      <x:c r="C10" s="67" t="str">
         <x:v>PL8304</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="str">
+      <x:c r="D10" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E10" s="67" t="str">
         <x:v>2026-05-14</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="str">
+      <x:c r="F10" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G10" s="30" t="n">
@@ -1086,19 +1446,19 @@
       <x:c r="A11" s="29" t="str">
         <x:v>W-B00-007</x:v>
       </x:c>
-      <x:c r="B11" s="39" t="str">
+      <x:c r="B11" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C11" s="39" t="str">
+      <x:c r="C11" s="67" t="str">
         <x:v>PL8304</x:v>
       </x:c>
-      <x:c r="D11" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="str">
+      <x:c r="D11" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E11" s="67" t="str">
         <x:v>2026-05-14</x:v>
       </x:c>
-      <x:c r="F11" s="39" t="str">
+      <x:c r="F11" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G11" s="30" t="n">
@@ -1109,19 +1469,19 @@
       <x:c r="A12" s="29" t="str">
         <x:v>W-B00-008</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="str">
+      <x:c r="B12" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="str">
+      <x:c r="C12" s="67" t="str">
         <x:v>VT8301</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="str">
+      <x:c r="D12" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E12" s="67" t="str">
         <x:v>2026-05-15</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="str">
+      <x:c r="F12" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G12" s="30" t="n">
@@ -1132,19 +1492,19 @@
       <x:c r="A13" s="29" t="str">
         <x:v>W-B00-009</x:v>
       </x:c>
-      <x:c r="B13" s="39" t="str">
+      <x:c r="B13" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C13" s="39" t="str">
+      <x:c r="C13" s="67" t="str">
         <x:v>VT8302</x:v>
       </x:c>
-      <x:c r="D13" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E13" s="39" t="str">
+      <x:c r="D13" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E13" s="67" t="str">
         <x:v>2026-05-15</x:v>
       </x:c>
-      <x:c r="F13" s="39" t="str">
+      <x:c r="F13" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G13" s="30" t="n">
@@ -1155,19 +1515,19 @@
       <x:c r="A14" s="29" t="str">
         <x:v>W-B00-010</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="str">
+      <x:c r="B14" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="str">
+      <x:c r="C14" s="67" t="str">
         <x:v>PL8305</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E14" s="39" t="str">
+      <x:c r="D14" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E14" s="67" t="str">
         <x:v>2026-05-16</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="str">
+      <x:c r="F14" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G14" s="30" t="n">
@@ -1178,19 +1538,19 @@
       <x:c r="A15" s="29" t="str">
         <x:v>W-B00-011</x:v>
       </x:c>
-      <x:c r="B15" s="39" t="str">
+      <x:c r="B15" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C15" s="39" t="str">
+      <x:c r="C15" s="67" t="str">
         <x:v>PL8306</x:v>
       </x:c>
-      <x:c r="D15" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E15" s="39" t="str">
+      <x:c r="D15" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E15" s="67" t="str">
         <x:v>2026-05-16</x:v>
       </x:c>
-      <x:c r="F15" s="39" t="str">
+      <x:c r="F15" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G15" s="30" t="n">
@@ -1201,19 +1561,19 @@
       <x:c r="A16" s="29" t="str">
         <x:v>W-B00-012</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="str">
+      <x:c r="B16" s="67" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="str">
+      <x:c r="C16" s="67" t="str">
         <x:v>PL8306</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E16" s="39" t="str">
+      <x:c r="D16" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E16" s="67" t="str">
         <x:v>2026-05-16</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="str">
+      <x:c r="F16" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G16" s="30" t="n">
@@ -1224,19 +1584,19 @@
       <x:c r="A17" s="29" t="str">
         <x:v>W-S01-001</x:v>
       </x:c>
-      <x:c r="B17" s="39" t="str">
+      <x:c r="B17" s="67" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="C17" s="39" t="str">
+      <x:c r="C17" s="67" t="str">
         <x:v>PL8307-TEST</x:v>
       </x:c>
-      <x:c r="D17" s="39" t="str">
+      <x:c r="D17" s="67" t="str">
         <x:v>MAT-S01-TP316L-001</x:v>
       </x:c>
-      <x:c r="E17" s="39" t="str">
+      <x:c r="E17" s="67" t="str">
         <x:v>2026-06-02</x:v>
       </x:c>
-      <x:c r="F17" s="39" t="str">
+      <x:c r="F17" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G17" s="30" t="n">
@@ -1247,19 +1607,19 @@
       <x:c r="A18" s="29" t="str">
         <x:v>W-S01-002</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="str">
+      <x:c r="B18" s="67" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="str">
+      <x:c r="C18" s="67" t="str">
         <x:v>PL8307-TEST</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="str">
+      <x:c r="D18" s="67" t="str">
         <x:v>MAT-S01-TP316L-001</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="str">
+      <x:c r="E18" s="67" t="str">
         <x:v>2026-06-02</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="str">
+      <x:c r="F18" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G18" s="30" t="n">
@@ -1270,19 +1630,19 @@
       <x:c r="A19" s="29" t="str">
         <x:v>W-S01-003</x:v>
       </x:c>
-      <x:c r="B19" s="39" t="str">
+      <x:c r="B19" s="67" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="C19" s="39" t="str">
+      <x:c r="C19" s="67" t="str">
         <x:v>PL8307-TEST</x:v>
       </x:c>
-      <x:c r="D19" s="39" t="str">
+      <x:c r="D19" s="67" t="str">
         <x:v>MAT-S01-NM01-001</x:v>
       </x:c>
-      <x:c r="E19" s="39" t="str">
+      <x:c r="E19" s="67" t="str">
         <x:v>2026-06-03</x:v>
       </x:c>
-      <x:c r="F19" s="39" t="str">
+      <x:c r="F19" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G19" s="30" t="n">
@@ -1293,19 +1653,19 @@
       <x:c r="A20" s="29" t="str">
         <x:v>W-S02-001</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="str">
+      <x:c r="B20" s="67" t="str">
         <x:v>S02</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="str">
+      <x:c r="C20" s="67" t="str">
         <x:v>PL8303</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="str">
+      <x:c r="D20" s="67" t="str">
         <x:v>MAT-S02-S30408-001</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="str">
+      <x:c r="E20" s="67" t="str">
         <x:v>2026-06-08</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="str">
+      <x:c r="F20" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G20" s="30" t="n">
@@ -1316,19 +1676,19 @@
       <x:c r="A21" s="29" t="str">
         <x:v>W-S02-002</x:v>
       </x:c>
-      <x:c r="B21" s="39" t="str">
+      <x:c r="B21" s="67" t="str">
         <x:v>S02</x:v>
       </x:c>
-      <x:c r="C21" s="39" t="str">
+      <x:c r="C21" s="67" t="str">
         <x:v>PL8303</x:v>
       </x:c>
-      <x:c r="D21" s="39" t="str">
+      <x:c r="D21" s="67" t="str">
         <x:v>MAT-S02-S30408-001</x:v>
       </x:c>
-      <x:c r="E21" s="39" t="str">
+      <x:c r="E21" s="67" t="str">
         <x:v>2026-06-08</x:v>
       </x:c>
-      <x:c r="F21" s="39" t="str">
+      <x:c r="F21" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G21" s="30" t="n">
@@ -1339,19 +1699,19 @@
       <x:c r="A22" s="29" t="str">
         <x:v>W-S02-003</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="str">
+      <x:c r="B22" s="67" t="str">
         <x:v>S02</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="str">
+      <x:c r="C22" s="67" t="str">
         <x:v>PL8303</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="str">
+      <x:c r="D22" s="67" t="str">
         <x:v>MAT-S02-S30408-001</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="str">
+      <x:c r="E22" s="67" t="str">
         <x:v>2026-06-09</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="str">
+      <x:c r="F22" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G22" s="30" t="n">
@@ -1362,19 +1722,19 @@
       <x:c r="A23" s="29" t="str">
         <x:v>W-S03-001</x:v>
       </x:c>
-      <x:c r="B23" s="39" t="str">
+      <x:c r="B23" s="67" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="C23" s="39" t="str">
+      <x:c r="C23" s="67" t="str">
         <x:v>ST8301-TEST</x:v>
       </x:c>
-      <x:c r="D23" s="39" t="str">
+      <x:c r="D23" s="67" t="str">
         <x:v>MAT-S03-15CRMO-001</x:v>
       </x:c>
-      <x:c r="E23" s="39" t="str">
+      <x:c r="E23" s="67" t="str">
         <x:v>2026-06-15</x:v>
       </x:c>
-      <x:c r="F23" s="39" t="str">
+      <x:c r="F23" s="67" t="str">
         <x:v>硬度合格</x:v>
       </x:c>
       <x:c r="G23" s="30" t="n">
@@ -1385,19 +1745,19 @@
       <x:c r="A24" s="29" t="str">
         <x:v>W-S03-002</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="str">
+      <x:c r="B24" s="67" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="str">
+      <x:c r="C24" s="67" t="str">
         <x:v>ST8301-TEST</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="str">
+      <x:c r="D24" s="67" t="str">
         <x:v>MAT-S03-15CRMO-001</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="str">
+      <x:c r="E24" s="67" t="str">
         <x:v>2026-06-15</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="str">
+      <x:c r="F24" s="67" t="str">
         <x:v>硬度合格</x:v>
       </x:c>
       <x:c r="G24" s="30" t="n">
@@ -1408,19 +1768,19 @@
       <x:c r="A25" s="29" t="str">
         <x:v>W-S03-003</x:v>
       </x:c>
-      <x:c r="B25" s="39" t="str">
+      <x:c r="B25" s="67" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="C25" s="39" t="str">
+      <x:c r="C25" s="67" t="str">
         <x:v>ST8301-TEST</x:v>
       </x:c>
-      <x:c r="D25" s="39" t="str">
+      <x:c r="D25" s="67" t="str">
         <x:v>MAT-S03-15CRMO-001</x:v>
       </x:c>
-      <x:c r="E25" s="39" t="str">
+      <x:c r="E25" s="67" t="str">
         <x:v>2026-06-16</x:v>
       </x:c>
-      <x:c r="F25" s="39" t="str">
+      <x:c r="F25" s="67" t="str">
         <x:v>返修后硬度合格</x:v>
       </x:c>
       <x:c r="G25" s="30" t="n">
@@ -1431,19 +1791,19 @@
       <x:c r="A26" s="29" t="str">
         <x:v>W-S03-004</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="str">
+      <x:c r="B26" s="67" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="str">
+      <x:c r="C26" s="67" t="str">
         <x:v>ST8301-TEST</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="str">
+      <x:c r="D26" s="67" t="str">
         <x:v>MAT-S03-15CRMO-001</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="str">
+      <x:c r="E26" s="67" t="str">
         <x:v>2026-06-16</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="str">
+      <x:c r="F26" s="67" t="str">
         <x:v>硬度合格</x:v>
       </x:c>
       <x:c r="G26" s="30" t="n">
@@ -1454,19 +1814,19 @@
       <x:c r="A27" s="29" t="str">
         <x:v>W-S04-001</x:v>
       </x:c>
-      <x:c r="B27" s="39" t="str">
+      <x:c r="B27" s="67" t="str">
         <x:v>S04</x:v>
       </x:c>
-      <x:c r="C27" s="39" t="str">
+      <x:c r="C27" s="67" t="str">
         <x:v>PL8308-TEST</x:v>
       </x:c>
-      <x:c r="D27" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E27" s="39" t="str">
+      <x:c r="D27" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E27" s="67" t="str">
         <x:v>2026-06-22</x:v>
       </x:c>
-      <x:c r="F27" s="39" t="str">
+      <x:c r="F27" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G27" s="30" t="n">
@@ -1477,19 +1837,19 @@
       <x:c r="A28" s="29" t="str">
         <x:v>W-S04-002</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="str">
+      <x:c r="B28" s="67" t="str">
         <x:v>S04</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="str">
+      <x:c r="C28" s="67" t="str">
         <x:v>PL8308-TEST</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E28" s="39" t="str">
+      <x:c r="D28" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E28" s="67" t="str">
         <x:v>2026-06-22</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="str">
+      <x:c r="F28" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G28" s="30" t="n">
@@ -1500,19 +1860,19 @@
       <x:c r="A29" s="29" t="str">
         <x:v>W-S04-003</x:v>
       </x:c>
-      <x:c r="B29" s="39" t="str">
+      <x:c r="B29" s="67" t="str">
         <x:v>S04</x:v>
       </x:c>
-      <x:c r="C29" s="39" t="str">
+      <x:c r="C29" s="67" t="str">
         <x:v>PL8308-TEST</x:v>
       </x:c>
-      <x:c r="D29" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E29" s="39" t="str">
+      <x:c r="D29" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E29" s="67" t="str">
         <x:v>2026-06-23</x:v>
       </x:c>
-      <x:c r="F29" s="39" t="str">
+      <x:c r="F29" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G29" s="30" t="n">
@@ -1523,19 +1883,19 @@
       <x:c r="A30" s="29" t="str">
         <x:v>W-S05-001</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="str">
+      <x:c r="B30" s="67" t="str">
         <x:v>S05</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="str">
+      <x:c r="C30" s="67" t="str">
         <x:v>PL8305</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E30" s="39" t="str">
+      <x:c r="D30" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E30" s="67" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="str">
+      <x:c r="F30" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G30" s="30" t="n">
@@ -1546,19 +1906,19 @@
       <x:c r="A31" s="29" t="str">
         <x:v>W-S05-002</x:v>
       </x:c>
-      <x:c r="B31" s="39" t="str">
+      <x:c r="B31" s="67" t="str">
         <x:v>S05</x:v>
       </x:c>
-      <x:c r="C31" s="39" t="str">
+      <x:c r="C31" s="67" t="str">
         <x:v>PL8305</x:v>
       </x:c>
-      <x:c r="D31" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E31" s="39" t="str">
+      <x:c r="D31" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E31" s="67" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="F31" s="39" t="str">
+      <x:c r="F31" s="67" t="str">
         <x:v>合格</x:v>
       </x:c>
       <x:c r="G31" s="30" t="n">
@@ -1569,19 +1929,19 @@
       <x:c r="A32" s="29" t="str">
         <x:v>W-S06-001</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="str">
+      <x:c r="B32" s="67" t="str">
         <x:v>S06</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="str">
+      <x:c r="C32" s="67" t="str">
         <x:v>PL8306</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E32" s="39" t="str">
+      <x:c r="D32" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E32" s="67" t="str">
         <x:v>2026-07-06</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="str">
+      <x:c r="F32" s="67" t="str">
         <x:v>RT/MT合格</x:v>
       </x:c>
       <x:c r="G32" s="30" t="n">
@@ -1592,19 +1952,19 @@
       <x:c r="A33" s="29" t="str">
         <x:v>W-S06-002</x:v>
       </x:c>
-      <x:c r="B33" s="39" t="str">
+      <x:c r="B33" s="67" t="str">
         <x:v>S06</x:v>
       </x:c>
-      <x:c r="C33" s="39" t="str">
+      <x:c r="C33" s="67" t="str">
         <x:v>PL8306</x:v>
       </x:c>
-      <x:c r="D33" s="39" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E33" s="39" t="str">
+      <x:c r="D33" s="67" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E33" s="67" t="str">
         <x:v>2026-07-06</x:v>
       </x:c>
-      <x:c r="F33" s="39" t="str">
+      <x:c r="F33" s="67" t="str">
         <x:v>RT/MT合格</x:v>
       </x:c>
       <x:c r="G33" s="30" t="n">
@@ -1615,19 +1975,19 @@
       <x:c r="A34" s="31" t="str">
         <x:v>W-S06-003</x:v>
       </x:c>
-      <x:c r="B34" s="40" t="str">
+      <x:c r="B34" s="68" t="str">
         <x:v>S06</x:v>
       </x:c>
-      <x:c r="C34" s="40" t="str">
+      <x:c r="C34" s="68" t="str">
         <x:v>PL8306</x:v>
       </x:c>
-      <x:c r="D34" s="40" t="str">
-        <x:v>MAT-B00-20-001</x:v>
-      </x:c>
-      <x:c r="E34" s="40" t="str">
+      <x:c r="D34" s="68" t="str">
+        <x:v>MAT-B00-20-001</x:v>
+      </x:c>
+      <x:c r="E34" s="68" t="str">
         <x:v>2026-07-07</x:v>
       </x:c>
-      <x:c r="F34" s="40" t="str">
+      <x:c r="F34" s="68" t="str">
         <x:v>RT/MT合格</x:v>
       </x:c>
       <x:c r="G34" s="32" t="n">
@@ -1635,11 +1995,51 @@
       </x:c>
     </x:row>
     <x:row r="35"/>
-    <x:row r="36"/>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="52" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B36" s="53"/>
+      <x:c r="C36" s="53"/>
+      <x:c r="D36" s="53"/>
+      <x:c r="E36" s="53"/>
+      <x:c r="F36" s="53"/>
+      <x:c r="G36" s="54"/>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="55"/>
+      <x:c r="B37" s="56"/>
+      <x:c r="C37" s="56"/>
+      <x:c r="D37" s="56"/>
+      <x:c r="E37" s="56"/>
+      <x:c r="F37" s="56"/>
+      <x:c r="G37" s="57"/>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="55"/>
+      <x:c r="B38" s="56"/>
+      <x:c r="C38" s="56"/>
+      <x:c r="D38" s="56"/>
+      <x:c r="E38" s="56"/>
+      <x:c r="F38" s="56"/>
+      <x:c r="G38" s="57"/>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="58"/>
+      <x:c r="B39" s="59"/>
+      <x:c r="C39" s="59"/>
+      <x:c r="D39" s="59"/>
+      <x:c r="E39" s="59"/>
+      <x:c r="F39" s="59"/>
+      <x:c r="G39" s="60"/>
+    </x:row>
+    <x:row r="40"/>
+    <x:row r="41"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A36:C36"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:G34">
     <x:cfRule type="expression" dxfId="4" priority="1">
@@ -1650,6 +2050,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b4a84877dcf487e"/>
 </x:worksheet>
 </file>
 
@@ -1704,13 +2105,13 @@
       <x:c r="A5" s="27" t="str">
         <x:v>MAT-B00-20-001</x:v>
       </x:c>
-      <x:c r="B5" s="38" t="str">
+      <x:c r="B5" s="66" t="str">
         <x:v>B00</x:v>
       </x:c>
-      <x:c r="C5" s="38" t="str">
+      <x:c r="C5" s="66" t="str">
         <x:v>20#</x:v>
       </x:c>
-      <x:c r="D5" s="38" t="str">
+      <x:c r="D5" s="66" t="str">
         <x:v>GB/T 8163</x:v>
       </x:c>
       <x:c r="E5" s="28" t="str">
@@ -1721,13 +2122,13 @@
       <x:c r="A6" s="29" t="str">
         <x:v>MAT-S01-TP316L-001</x:v>
       </x:c>
-      <x:c r="B6" s="39" t="str">
+      <x:c r="B6" s="67" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="C6" s="39" t="str">
+      <x:c r="C6" s="67" t="str">
         <x:v>ASTM A312 TP316L</x:v>
       </x:c>
-      <x:c r="D6" s="39" t="str">
+      <x:c r="D6" s="67" t="str">
         <x:v>ASTM A312/A312M</x:v>
       </x:c>
       <x:c r="E6" s="30" t="str">
@@ -1738,13 +2139,13 @@
       <x:c r="A7" s="29" t="str">
         <x:v>MAT-S01-NM01-001</x:v>
       </x:c>
-      <x:c r="B7" s="39" t="str">
+      <x:c r="B7" s="67" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="C7" s="39" t="str">
+      <x:c r="C7" s="67" t="str">
         <x:v>TEST-NM01</x:v>
       </x:c>
-      <x:c r="D7" s="39" t="str">
+      <x:c r="D7" s="67" t="str">
         <x:v>TEST-QX-NM01-2026</x:v>
       </x:c>
       <x:c r="E7" s="30" t="str">
@@ -1755,13 +2156,13 @@
       <x:c r="A8" s="29" t="str">
         <x:v>MAT-S02-S30408-001</x:v>
       </x:c>
-      <x:c r="B8" s="39" t="str">
+      <x:c r="B8" s="67" t="str">
         <x:v>S02</x:v>
       </x:c>
-      <x:c r="C8" s="39" t="str">
+      <x:c r="C8" s="67" t="str">
         <x:v>S30408</x:v>
       </x:c>
-      <x:c r="D8" s="39" t="str">
+      <x:c r="D8" s="67" t="str">
         <x:v>GB/T 14976</x:v>
       </x:c>
       <x:c r="E8" s="30" t="str">
@@ -1772,13 +2173,13 @@
       <x:c r="A9" s="31" t="str">
         <x:v>MAT-S03-15CRMO-001</x:v>
       </x:c>
-      <x:c r="B9" s="40" t="str">
+      <x:c r="B9" s="68" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="C9" s="40" t="str">
+      <x:c r="C9" s="68" t="str">
         <x:v>15CrMoG</x:v>
       </x:c>
-      <x:c r="D9" s="40" t="str">
+      <x:c r="D9" s="68" t="str">
         <x:v>GB/T 5310</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
@@ -1786,11 +2187,43 @@
       </x:c>
     </x:row>
     <x:row r="10"/>
-    <x:row r="11"/>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="52" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B11" s="53"/>
+      <x:c r="C11" s="53"/>
+      <x:c r="D11" s="53"/>
+      <x:c r="E11" s="54"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="55"/>
+      <x:c r="B12" s="56"/>
+      <x:c r="C12" s="56"/>
+      <x:c r="D12" s="56"/>
+      <x:c r="E12" s="57"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="55"/>
+      <x:c r="B13" s="56"/>
+      <x:c r="C13" s="56"/>
+      <x:c r="D13" s="56"/>
+      <x:c r="E13" s="57"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="58"/>
+      <x:c r="B14" s="59"/>
+      <x:c r="C14" s="59"/>
+      <x:c r="D14" s="59"/>
+      <x:c r="E14" s="60"/>
+    </x:row>
+    <x:row r="15"/>
+    <x:row r="16"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A11:C11"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:E9">
     <x:cfRule type="expression" dxfId="6" priority="1">
@@ -1801,6 +2234,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e21671dc3d04fc9"/>
 </x:worksheet>
 </file>
 
@@ -1810,8 +2244,9 @@
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24.440000534057617" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" hidden="0" customHeight="1">
@@ -1821,6 +2256,7 @@
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
       <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
     </x:row>
     <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -1829,6 +2265,7 @@
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
     </x:row>
     <x:row r="3"/>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -1849,10 +2286,10 @@
       <x:c r="A5" s="27" t="str">
         <x:v>OWNER-HJDX</x:v>
       </x:c>
-      <x:c r="B5" s="38" t="str">
+      <x:c r="B5" s="66" t="str">
         <x:v>珠海恒基达鑫国际化工仓储股份有限公司</x:v>
       </x:c>
-      <x:c r="C5" s="38" t="str">
+      <x:c r="C5" s="66" t="str">
         <x:v>建设单位</x:v>
       </x:c>
       <x:c r="D5" s="28" t="str">
@@ -1863,10 +2300,10 @@
       <x:c r="A6" s="29" t="str">
         <x:v>DESIGN-XR</x:v>
       </x:c>
-      <x:c r="B6" s="39" t="str">
+      <x:c r="B6" s="67" t="str">
         <x:v>广东星燃石化设计院有限公司</x:v>
       </x:c>
-      <x:c r="C6" s="39" t="str">
+      <x:c r="C6" s="67" t="str">
         <x:v>设计单位</x:v>
       </x:c>
       <x:c r="D6" s="30" t="str">
@@ -1875,97 +2312,97 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="29" t="str">
-        <x:v>TEST-INSTALLATION-ORG</x:v>
-      </x:c>
-      <x:c r="B7" s="39" t="str">
-        <x:v>TEST-压力管道安装单位</x:v>
-      </x:c>
-      <x:c r="C7" s="39" t="str">
-        <x:v>施工单位</x:v>
+        <x:v>INSTALL-GZHG</x:v>
+      </x:c>
+      <x:c r="B7" s="67" t="str">
+        <x:v>贵州化工建设有限责任公司</x:v>
+      </x:c>
+      <x:c r="C7" s="67" t="str">
+        <x:v>2021年施工单位</x:v>
       </x:c>
       <x:c r="D7" s="30" t="str">
-        <x:v>合成</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+        <x:v>来源复用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A8" s="29" t="str">
-        <x:v>TEST-NDT-ORG</x:v>
-      </x:c>
-      <x:c r="B8" s="39" t="str">
-        <x:v>TEST-无损检测机构</x:v>
-      </x:c>
-      <x:c r="C8" s="39" t="str">
-        <x:v>无损检测单位</x:v>
+        <x:v>NDT-NJJX</x:v>
+      </x:c>
+      <x:c r="B8" s="67" t="str">
+        <x:v>南京金鑫检测工程有限责任公司</x:v>
+      </x:c>
+      <x:c r="C8" s="67" t="str">
+        <x:v>交工资料登记无损检测单位</x:v>
       </x:c>
       <x:c r="D8" s="30" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="29" t="str">
-        <x:v>TEST-LAB-ORG</x:v>
-      </x:c>
-      <x:c r="B9" s="39" t="str">
-        <x:v>TEST-材料与理化试验机构</x:v>
-      </x:c>
-      <x:c r="C9" s="39" t="str">
-        <x:v>试验单位</x:v>
+        <x:v>NDT-GZSH</x:v>
+      </x:c>
+      <x:c r="B9" s="67" t="str">
+        <x:v>广州声华科技股份有限公司</x:v>
+      </x:c>
+      <x:c r="C9" s="67" t="str">
+        <x:v>2021年RT报告签发单位</x:v>
       </x:c>
       <x:c r="D9" s="30" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="29" t="str">
-        <x:v>TEST-SUPERVISION-ORG</x:v>
-      </x:c>
-      <x:c r="B10" s="39" t="str">
-        <x:v>TEST-监督检验角色单位</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="str">
-        <x:v>监检角色</x:v>
+        <x:v>SUPV-GD-ZH</x:v>
+      </x:c>
+      <x:c r="B10" s="67" t="str">
+        <x:v>广东省特种设备检测研究院珠海检测院</x:v>
+      </x:c>
+      <x:c r="C10" s="67" t="str">
+        <x:v>2021年安装监督检验单位</x:v>
       </x:c>
       <x:c r="D10" s="30" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="29" t="str">
-        <x:v>TEST-PER-DES-01</x:v>
-      </x:c>
-      <x:c r="B11" s="39" t="str">
-        <x:v>测试设计负责人甲</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="str">
-        <x:v>设计</x:v>
+        <x:v>MFR-GH</x:v>
+      </x:c>
+      <x:c r="B11" s="67" t="str">
+        <x:v>河北广浩管件有限公司</x:v>
+      </x:c>
+      <x:c r="C11" s="67" t="str">
+        <x:v>来源管件制造单位</x:v>
       </x:c>
       <x:c r="D11" s="30" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="29" t="str">
-        <x:v>TEST-PER-CHK-01</x:v>
-      </x:c>
-      <x:c r="B12" s="39" t="str">
-        <x:v>测试校核负责人乙</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="str">
-        <x:v>校核</x:v>
+        <x:v>MFR-LB</x:v>
+      </x:c>
+      <x:c r="B12" s="67" t="str">
+        <x:v>烟台鲁宝钢管有限责任公司</x:v>
+      </x:c>
+      <x:c r="C12" s="67" t="str">
+        <x:v>来源钢管制造单位</x:v>
       </x:c>
       <x:c r="D12" s="30" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="29" t="str">
-        <x:v>TEST-PER-APR-01</x:v>
-      </x:c>
-      <x:c r="B13" s="39" t="str">
-        <x:v>测试批准负责人丙</x:v>
-      </x:c>
-      <x:c r="C13" s="39" t="str">
-        <x:v>批准</x:v>
+        <x:v>TEST-INSTALLATION-ORG</x:v>
+      </x:c>
+      <x:c r="B13" s="67" t="str">
+        <x:v>TEST-压力管道安装单位</x:v>
+      </x:c>
+      <x:c r="C13" s="67" t="str">
+        <x:v>施工单位</x:v>
       </x:c>
       <x:c r="D13" s="30" t="str">
         <x:v>合成</x:v>
@@ -1973,13 +2410,13 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="29" t="str">
-        <x:v>TEST-PER-QA-01</x:v>
-      </x:c>
-      <x:c r="B14" s="39" t="str">
-        <x:v>测试质量责任人员丁</x:v>
-      </x:c>
-      <x:c r="C14" s="39" t="str">
-        <x:v>质量保证</x:v>
+        <x:v>TEST-NDT-ORG</x:v>
+      </x:c>
+      <x:c r="B14" s="67" t="str">
+        <x:v>TEST-无损检测机构</x:v>
+      </x:c>
+      <x:c r="C14" s="67" t="str">
+        <x:v>无损检测单位</x:v>
       </x:c>
       <x:c r="D14" s="30" t="str">
         <x:v>合成</x:v>
@@ -1987,40 +2424,212 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="29" t="str">
-        <x:v>TEST-PER-WELD-01</x:v>
-      </x:c>
-      <x:c r="B15" s="39" t="str">
-        <x:v>测试焊工甲</x:v>
-      </x:c>
-      <x:c r="C15" s="39" t="str">
-        <x:v>焊工</x:v>
+        <x:v>TEST-LAB-ORG</x:v>
+      </x:c>
+      <x:c r="B15" s="67" t="str">
+        <x:v>TEST-材料与理化试验机构</x:v>
+      </x:c>
+      <x:c r="C15" s="67" t="str">
+        <x:v>试验单位</x:v>
       </x:c>
       <x:c r="D15" s="30" t="str">
         <x:v>合成</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="31" t="str">
+      <x:c r="A16" s="29" t="str">
+        <x:v>TEST-SUPERVISION-ORG</x:v>
+      </x:c>
+      <x:c r="B16" s="67" t="str">
+        <x:v>TEST-监督检验角色单位</x:v>
+      </x:c>
+      <x:c r="C16" s="67" t="str">
+        <x:v>监检角色</x:v>
+      </x:c>
+      <x:c r="D16" s="30" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="29" t="str">
+        <x:v>PER-YDH</x:v>
+      </x:c>
+      <x:c r="B17" s="67" t="str">
+        <x:v>杨道红</x:v>
+      </x:c>
+      <x:c r="C17" s="67" t="str">
+        <x:v>来源设计许可印章人员</x:v>
+      </x:c>
+      <x:c r="D17" s="30" t="str">
+        <x:v>来源复用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="29" t="str">
+        <x:v>PER-ZWH</x:v>
+      </x:c>
+      <x:c r="B18" s="67" t="str">
+        <x:v>赵伟辉</x:v>
+      </x:c>
+      <x:c r="C18" s="67" t="str">
+        <x:v>2021年交工记录焊工</x:v>
+      </x:c>
+      <x:c r="D18" s="30" t="str">
+        <x:v>来源复用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="29" t="str">
+        <x:v>PER-PBX</x:v>
+      </x:c>
+      <x:c r="B19" s="67" t="str">
+        <x:v>庞柏鑫</x:v>
+      </x:c>
+      <x:c r="C19" s="67" t="str">
+        <x:v>2021年交工记录焊工</x:v>
+      </x:c>
+      <x:c r="D19" s="30" t="str">
+        <x:v>来源复用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="29" t="str">
+        <x:v>PER-ZJX</x:v>
+      </x:c>
+      <x:c r="B20" s="67" t="str">
+        <x:v>赵俊祥</x:v>
+      </x:c>
+      <x:c r="C20" s="67" t="str">
+        <x:v>来源焊工资格证人员</x:v>
+      </x:c>
+      <x:c r="D20" s="30" t="str">
+        <x:v>来源复用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="29" t="str">
+        <x:v>TEST-PER-DES-01</x:v>
+      </x:c>
+      <x:c r="B21" s="67" t="str">
+        <x:v>测试设计负责人甲</x:v>
+      </x:c>
+      <x:c r="C21" s="67" t="str">
+        <x:v>设计</x:v>
+      </x:c>
+      <x:c r="D21" s="30" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="29" t="str">
+        <x:v>TEST-PER-CHK-01</x:v>
+      </x:c>
+      <x:c r="B22" s="67" t="str">
+        <x:v>测试校核负责人乙</x:v>
+      </x:c>
+      <x:c r="C22" s="67" t="str">
+        <x:v>校核</x:v>
+      </x:c>
+      <x:c r="D22" s="30" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="29" t="str">
+        <x:v>TEST-PER-APR-01</x:v>
+      </x:c>
+      <x:c r="B23" s="67" t="str">
+        <x:v>测试批准负责人丙</x:v>
+      </x:c>
+      <x:c r="C23" s="67" t="str">
+        <x:v>批准</x:v>
+      </x:c>
+      <x:c r="D23" s="30" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="29" t="str">
+        <x:v>TEST-PER-QA-01</x:v>
+      </x:c>
+      <x:c r="B24" s="67" t="str">
+        <x:v>测试质量责任人员丁</x:v>
+      </x:c>
+      <x:c r="C24" s="67" t="str">
+        <x:v>质量保证</x:v>
+      </x:c>
+      <x:c r="D24" s="30" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="29" t="str">
+        <x:v>TEST-PER-WELD-01</x:v>
+      </x:c>
+      <x:c r="B25" s="67" t="str">
+        <x:v>测试焊工甲</x:v>
+      </x:c>
+      <x:c r="C25" s="67" t="str">
+        <x:v>焊工</x:v>
+      </x:c>
+      <x:c r="D25" s="30" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="31" t="str">
         <x:v>TEST-PER-NDT-01</x:v>
       </x:c>
-      <x:c r="B16" s="40" t="str">
+      <x:c r="B26" s="68" t="str">
         <x:v>测试检测人员乙</x:v>
       </x:c>
-      <x:c r="C16" s="40" t="str">
+      <x:c r="C26" s="68" t="str">
         <x:v>无损检测</x:v>
       </x:c>
-      <x:c r="D16" s="32" t="str">
+      <x:c r="D26" s="32" t="str">
         <x:v>合成</x:v>
       </x:c>
     </x:row>
-    <x:row r="17"/>
-    <x:row r="18"/>
+    <x:row r="27"/>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="52" t="str">
+        <x:v>电子签署（测试）｜资料验收测试专用章</x:v>
+      </x:c>
+      <x:c r="B28" s="53"/>
+      <x:c r="C28" s="53"/>
+      <x:c r="D28" s="53"/>
+      <x:c r="E28" s="54"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="55"/>
+      <x:c r="B29" s="56"/>
+      <x:c r="C29" s="56"/>
+      <x:c r="D29" s="56"/>
+      <x:c r="E29" s="57"/>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="55"/>
+      <x:c r="B30" s="56"/>
+      <x:c r="C30" s="56"/>
+      <x:c r="D30" s="56"/>
+      <x:c r="E30" s="57"/>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="58"/>
+      <x:c r="B31" s="59"/>
+      <x:c r="C31" s="59"/>
+      <x:c r="D31" s="59"/>
+      <x:c r="E31" s="60"/>
+    </x:row>
+    <x:row r="32"/>
+    <x:row r="33"/>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A28:C28"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:D16">
+  <x:conditionalFormatting sqref="A5:D26">
     <x:cfRule type="expression" dxfId="8" priority="1">
       <x:formula>OR(ISNUMBER(SEARCH("不合格",A5)),ISNUMBER(SEARCH("异常",A5)))</x:formula>
     </x:cfRule>
@@ -2029,5 +2638,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7555fdc733c641d4"/>
 </x:worksheet>
 </file>